--- a/extra_files/list_tfrecord.xlsx
+++ b/extra_files/list_tfrecord.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar.medinaculma\Documents\git\UG100\extra_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B235CCC-F0E1-4276-876C-D4CA4E74577D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD264E80-4F5A-47C5-B960-BF7AA690E564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8970" yWindow="1500" windowWidth="25710" windowHeight="15345" xr2:uid="{8510993A-3006-411E-A8D3-9802DF10AA14}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{8510993A-3006-411E-A8D3-9802DF10AA14}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="100">
   <si>
     <t>exampleFile</t>
   </si>
@@ -162,13 +164,190 @@
   </si>
   <si>
     <t>/90daydata/xu_alfalfabreeding/system_from_home/msi/UG100/08_make_examples/0040.tfrecord</t>
+  </si>
+  <si>
+    <t>RegenSY27</t>
+  </si>
+  <si>
+    <t>GENOME_TERRITORY</t>
+  </si>
+  <si>
+    <t>PCT_EXC_MAPQ</t>
+  </si>
+  <si>
+    <t>PCT_EXC_UNPAIRED</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Haplo_1</t>
+  </si>
+  <si>
+    <t>Phased_1:4</t>
+  </si>
+  <si>
+    <t>extra_information</t>
+  </si>
+  <si>
+    <t>[+] extra_information {}</t>
+  </si>
+  <si>
+    <t>n_bytes</t>
+  </si>
+  <si>
+    <t>n_records</t>
+  </si>
+  <si>
+    <t>total_reads</t>
+  </si>
+  <si>
+    <t>total_aligned_reads</t>
+  </si>
+  <si>
+    <t>total_bases</t>
+  </si>
+  <si>
+    <t>total_aligned_bases</t>
+  </si>
+  <si>
+    <t>total_softclipped_bases</t>
+  </si>
+  <si>
+    <t>bqual</t>
+  </si>
+  <si>
+    <t>[+] bqual[36]</t>
+  </si>
+  <si>
+    <t>pf_bqual</t>
+  </si>
+  <si>
+    <t>[+] pf_bqual[36]</t>
+  </si>
+  <si>
+    <t>read_length</t>
+  </si>
+  <si>
+    <t>[+] read_length[521]</t>
+  </si>
+  <si>
+    <t>pf_read_length</t>
+  </si>
+  <si>
+    <t>[+] pf_read_length[521]</t>
+  </si>
+  <si>
+    <t>aligned_read_length</t>
+  </si>
+  <si>
+    <t>[+] aligned_read_length[521]</t>
+  </si>
+  <si>
+    <t>pf_bases</t>
+  </si>
+  <si>
+    <t>pf_reads</t>
+  </si>
+  <si>
+    <t>pf_aligned_bases</t>
+  </si>
+  <si>
+    <t>pf_aligned_reads</t>
+  </si>
+  <si>
+    <t>pf_hq_aligned_reads</t>
+  </si>
+  <si>
+    <t>pf_hq_aligned_bases</t>
+  </si>
+  <si>
+    <t>pf_hq_aligned_split_reads</t>
+  </si>
+  <si>
+    <t>nr_very_long_reads</t>
+  </si>
+  <si>
+    <t>nr_discarded_reads</t>
+  </si>
+  <si>
+    <t>nr_duplicate_reads</t>
+  </si>
+  <si>
+    <t>mapq</t>
+  </si>
+  <si>
+    <t>[+] mapq[61]</t>
+  </si>
+  <si>
+    <t>bqx</t>
+  </si>
+  <si>
+    <t>[+] bqx[520]</t>
+  </si>
+  <si>
+    <t>pf_mismatch_bases</t>
+  </si>
+  <si>
+    <t>pf_indel_events</t>
+  </si>
+  <si>
+    <t>nr_optical_false_detected</t>
+  </si>
+  <si>
+    <t>nr_optical_ring_overlap</t>
+  </si>
+  <si>
+    <t>base_coverage</t>
+  </si>
+  <si>
+    <t>[+] base_coverage {}</t>
+  </si>
+  <si>
+    <t>cvg</t>
+  </si>
+  <si>
+    <t>[+] cvg[10001]</t>
+  </si>
+  <si>
+    <t>[-] extra_information {}</t>
+  </si>
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>S18-NGX</t>
+  </si>
+  <si>
+    <t>barcode</t>
+  </si>
+  <si>
+    <t>Z0018</t>
+  </si>
+  <si>
+    <t>minor_rg</t>
+  </si>
+  <si>
+    <t>sequence</t>
+  </si>
+  <si>
+    <t>CATGCGTCCTGTGAT</t>
+  </si>
+  <si>
+    <t>Stats 01</t>
+  </si>
+  <si>
+    <t>CRAM 02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,16 +361,51 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF234A97"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF234A97"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0B6125"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Primeicons"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -199,13 +413,182 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC5C5C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFEDEDED"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC5C5C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFEDEDED"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFEDEDED"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC5C5C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC5C5C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFEDEDED"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC5C5C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFEDEDED"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFEDEDED"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFEDEDED"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFEDEDED"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC5C5C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFEDEDED"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFEDEDED"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC5C5C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFEDEDED"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFEDEDED"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC5C5C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFEDEDED"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC5C5C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFEDEDED"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC5C5C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC5C5C5"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFC5C5C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFC5C5C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC5C5C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC5C5C5"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC5C5C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFC5C5C5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC5C5C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -543,13 +926,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C310B1BB-4533-48BD-B8D5-1693EC32F631}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="88.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -563,7 +946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,7 +960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -591,7 +974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -605,7 +988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -619,7 +1002,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,7 +1016,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -647,7 +1030,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,7 +1044,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +1058,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -689,7 +1072,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -703,7 +1086,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -717,7 +1100,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -731,7 +1114,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -745,7 +1128,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -759,7 +1142,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -773,7 +1156,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -787,7 +1170,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,7 +1184,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -815,7 +1198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
@@ -829,7 +1212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
@@ -843,7 +1226,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -857,7 +1240,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
         <v>0</v>
       </c>
@@ -871,7 +1254,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -885,7 +1268,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -899,7 +1282,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -913,7 +1296,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -927,7 +1310,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
@@ -941,7 +1324,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -955,7 +1338,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -969,7 +1352,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -983,7 +1366,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -997,7 +1380,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -1011,7 +1394,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -1025,7 +1408,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -1039,7 +1422,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
@@ -1053,7 +1436,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1450,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -1081,7 +1464,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -1095,7 +1478,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -1113,4 +1496,484 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DAFB635-A060-49B3-B683-9761AE83568C}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5" ht="17.25">
+      <c r="A1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2">
+        <v>653356514</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.374861</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0.625139</v>
+      </c>
+      <c r="E2" s="3">
+        <f>SUM(C2:D2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3">
+        <v>2594267024</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.62834599999999996</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.37165399999999998</v>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM(C3:D3)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{008F1281-0B24-4210-9CA0-CB7F938A7F01}">
+  <dimension ref="A1:N34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="11"/>
+      <c r="G1" s="12"/>
+      <c r="M1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1">
+        <v>1842130482480</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2">
+        <v>1842130482480</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="G2" s="14"/>
+      <c r="M2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N2">
+        <v>1054270369</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3">
+        <v>1054270369</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="M3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3">
+        <v>998463718</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4">
+        <v>998463718</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="M4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4">
+        <v>993474262</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5">
+        <v>993474262</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="M5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5">
+        <v>297354215135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6">
+        <v>297354215135</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="M6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N6">
+        <v>295954758220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <v>295954758220</v>
+      </c>
+      <c r="M7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7">
+        <v>35014717852</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8">
+        <v>35014717852</v>
+      </c>
+      <c r="M8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" t="s">
+        <v>62</v>
+      </c>
+      <c r="N10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13" t="s">
+        <v>68</v>
+      </c>
+      <c r="N13">
+        <v>297354215135</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14">
+        <v>297354215135</v>
+      </c>
+      <c r="M14" t="s">
+        <v>69</v>
+      </c>
+      <c r="N14">
+        <v>998463718</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15">
+        <v>998463718</v>
+      </c>
+      <c r="M15" t="s">
+        <v>70</v>
+      </c>
+      <c r="N15">
+        <v>259653429580</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16">
+        <v>259653429580</v>
+      </c>
+      <c r="M16" t="s">
+        <v>71</v>
+      </c>
+      <c r="N16">
+        <v>993474262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17">
+        <v>993474262</v>
+      </c>
+      <c r="M17" t="s">
+        <v>72</v>
+      </c>
+      <c r="N17">
+        <v>356133001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18">
+        <v>356133001</v>
+      </c>
+      <c r="M18" t="s">
+        <v>73</v>
+      </c>
+      <c r="N18">
+        <v>97243792957</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19">
+        <v>97243792957</v>
+      </c>
+      <c r="M19" t="s">
+        <v>74</v>
+      </c>
+      <c r="N19">
+        <v>14123422</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20">
+        <v>14123422</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23">
+        <v>165618594</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26">
+        <v>2443263480</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27">
+        <v>2017487522</v>
+      </c>
+      <c r="N27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28">
+        <v>2500563</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29">
+        <v>4074</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/extra_files/list_tfrecord.xlsx
+++ b/extra_files/list_tfrecord.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cesar.medinaculma\Documents\git\UG100\extra_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD264E80-4F5A-47C5-B960-BF7AA690E564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F2F3EA-D8B9-4B32-9182-A6A42040BD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{8510993A-3006-411E-A8D3-9802DF10AA14}"/>
+    <workbookView xWindow="14580" yWindow="3975" windowWidth="25275" windowHeight="8385" activeTab="3" xr2:uid="{8510993A-3006-411E-A8D3-9802DF10AA14}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="109">
   <si>
     <t>exampleFile</t>
   </si>
@@ -338,6 +339,33 @@
   </si>
   <si>
     <t>CRAM 02</t>
+  </si>
+  <si>
+    <t>Sub-Total</t>
+  </si>
+  <si>
+    <t>Total (Phased_1:4)</t>
+  </si>
+  <si>
+    <t>Chr</t>
+  </si>
+  <si>
+    <t>medsa.RegenSY27x.gnm1</t>
+  </si>
+  <si>
+    <t>Genome</t>
+  </si>
+  <si>
+    <t>Chr_.1</t>
+  </si>
+  <si>
+    <t>Chr_.2</t>
+  </si>
+  <si>
+    <t>Chr_.3</t>
+  </si>
+  <si>
+    <t>Chr_.4</t>
   </si>
 </sst>
 </file>
@@ -1976,4 +2004,223 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BD650B6-E0E6-4EB6-BF41-82F0C67487B2}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>85129743</v>
+      </c>
+      <c r="D2">
+        <v>87534413</v>
+      </c>
+      <c r="E2">
+        <v>86698797</v>
+      </c>
+      <c r="F2">
+        <v>81593309</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>69581426</v>
+      </c>
+      <c r="D3">
+        <v>69606329</v>
+      </c>
+      <c r="E3">
+        <v>75653446</v>
+      </c>
+      <c r="F3">
+        <v>72621877</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>96190425</v>
+      </c>
+      <c r="D4">
+        <v>90827970</v>
+      </c>
+      <c r="E4">
+        <v>91408138</v>
+      </c>
+      <c r="F4">
+        <v>83189900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>83716887</v>
+      </c>
+      <c r="D5">
+        <v>83291558</v>
+      </c>
+      <c r="E5">
+        <v>86231604</v>
+      </c>
+      <c r="F5">
+        <v>92808212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>79699470</v>
+      </c>
+      <c r="D6">
+        <v>62554310</v>
+      </c>
+      <c r="E6">
+        <v>75148351</v>
+      </c>
+      <c r="F6">
+        <v>71615600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>83742631</v>
+      </c>
+      <c r="D7">
+        <v>73507436</v>
+      </c>
+      <c r="E7">
+        <v>69463442</v>
+      </c>
+      <c r="F7">
+        <v>82998842</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>79053817</v>
+      </c>
+      <c r="D8">
+        <v>87713645</v>
+      </c>
+      <c r="E8">
+        <v>88635038</v>
+      </c>
+      <c r="F8">
+        <v>96423042</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>76300915</v>
+      </c>
+      <c r="D9">
+        <v>70660710</v>
+      </c>
+      <c r="E9">
+        <v>74845475</v>
+      </c>
+      <c r="F9">
+        <v>86071966</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10">
+        <v>653415314</v>
+      </c>
+      <c r="D10">
+        <v>625696371</v>
+      </c>
+      <c r="E10">
+        <v>648084291</v>
+      </c>
+      <c r="F10">
+        <v>667322748</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11">
+        <v>2594518724</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>